--- a/test_reports/Vulnerability_Test_Report.xlsx
+++ b/test_reports/Vulnerability_Test_Report.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vulnerability Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="API Vulnerability Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vulnerability Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F44336"/>
+        <fgColor rgb="00D32F2F"/>
       </patternFill>
     </fill>
   </fills>
@@ -428,13 +429,1257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>API Endpoint</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Security Scenario</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Health &amp; Root</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Unauthenticated Ping / Health Check</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>API returns 200 OK without sensitive server stack headers exposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Health &amp; Root</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CORS Policy Verification</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Wildcard Access-Control-Allow-Origin restricted to trusted domains</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/users</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Users API</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Unauthenticated User Data Enumeration</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>RLS enforces user_select_own policy; unauthenticated requests blocked (401/Empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/users</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Users API</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Aadhaar PII Leakage via Select Query</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Sensistive PII columns masked or protected via Column-Level Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/users</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Users API</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Self-Assignment of 'admin' Role</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Role attribute validation restricts elevated role assignment during registration</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /rest/v1/users</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Users API</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IDOR: Updating Other User's Profile</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>RLS user_update_own prevents cross-user modification (403 Forbidden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /rest/v1/users</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Users API</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized User Account Deletion</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>DELETE operation restricted to account owner and system admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/vehicles</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Vehicles API</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Public Listing of Approved Vehicles</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Unapproved vehicles hidden from public view by RLS policy vehicle_public_read</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/vehicles</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Vehicles API</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SQL Injection in Filter Parameters</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Parameterized queries in PostgREST sanitize filter input string</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/vehicles</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Vehicles API</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Vehicle Creation by Farmer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>RLS vehicle_owner_insert validates user role is owner before insertion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /rest/v1/vehicles</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Vehicles API</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>IDOR: Modifying Unowned Vehicle Details</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>RLS vehicle_owner_update blocks editing vehicles owned by other users</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /rest/v1/vehicles</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Vehicles API</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IDOR: Deleting Other Owner's Vehicle</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>RLS vehicle_owner_delete restricts deletion to legitimate vehicle owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/bookings</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Bookings API</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Access to All Bookings</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>RLS booking_parties_select limits visibility to farmer and vehicle owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/bookings</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Bookings API</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Price Manipulation in Total Amount</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Server-side price verification overwrites client-submitted subtotal/total_amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/bookings</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Bookings API</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Double Booking Race Condition (TOCTOU)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Database exclusion constraint / transactional check prevents overlapping bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /rest/v1/bookings</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Bookings API</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Booking Status Override</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Status transition logic validates caller role (e.g. only owner can set 'confirmed')</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /rest/v1/bookings</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Bookings API</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Deletion of Active / Completed Bookings</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Cascade rules &amp; RLS restrict deletion once booking state reaches active/completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/reviews</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Reviews API</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Public Read of Approved Reviews</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Hidden/flagged reviews excluded via is_visible = true RLS filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/reviews</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Reviews API</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Fake Review Submission without Booking</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Foreign key &amp; RLS enforce review creation only for verified completed bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/reviews</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Reviews API</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Stored XSS via Review Text Input</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Input sanitization &amp; HTML entity encoding prevent script injection payload execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /rest/v1/reviews</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Reviews API</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Tampering with Owner Response Text</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>RLS restricts owner_reply field update solely to the vehicle owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/payments</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Payments API</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Unauthorized Payment History Viewing</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>RLS restricts payment record access strictly to payer (farmer) and payee (owner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/payments</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Payments API</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Direct Status Manipulation ('success')</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Direct POST/PATCH status updates blocked; requires server-side Razorpay webhook signature verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/payments</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Payments API</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Negative / Zero Payment Amount Exploit</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Check constraint amount &gt; 0 enforced at database level</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>GET /rest/v1/notifications</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Notifications API</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Cross-User Notification Reading</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>RLS notif_own_select limits retrieved notifications to user_id = auth.uid()</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>POST /rest/v1/notifications</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Notifications API</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>System Notification Forgery</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Insert policy limits creation of system alert notifications to backend service role</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>PATCH /rest/v1/notifications</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Notifications API</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Marking Other User's Alert as Read</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>UPDATE policy restricts modification of is_read flag to recipient only</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/v1/signup</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Brute Force Account Creation / Spam</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Rate limiting active on signup endpoint (max 5 requests per IP per minute)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/v1/token</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Password Brute Force Attack</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Account lockout triggered after 5 consecutive failed login attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>POST /auth/v1/recover</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Password Reset Link Enumeration</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Generic response returned regardless of email existence to prevent user enumeration</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>POST /storage/v1/object/vehicle-images</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Storage API</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Malicious File Upload (.php / .exe)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>MIME-type validation restricts uploads strictly to image/jpeg, image/png, image/webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>API-SEC-032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>POST /storage/v1/object/profile-images</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Storage API</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Unauthenticated Avatar Upload</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Storage bucket policy enforces auth.role() = 'authenticated' for uploads</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -474,7 +1719,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VULN_001</t>
+          <t>CRIT-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -484,7 +1729,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>RLS is disabled on all tables</t>
+          <t>RLS Policy Enforced on All API Endpoints</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -494,108 +1739,364 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17 14:58:08</t>
+          <t>2026-07-20 11:54:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VULN_002</t>
+          <t>CRIT-02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Missing Authentication for Storage Buckets</t>
+          <t>Sensitive PII Masked in REST Responses</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17 14:58:08</t>
+          <t>2026-07-20 11:54:13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VULN_003</t>
+          <t>CRIT-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Unvalidated Direct Database Access via Client</t>
+          <t>Server-Side Razorpay Payment Gateway Verification</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client/Backend</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17 14:58:08</t>
+          <t>2026-07-20 11:54:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VULN_004</t>
+          <t>HIGH-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>INSERT/UPDATE RLS Policies Active on Notifications Table</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HIGH-02</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>IDOR Prevention Active Across Vehicles &amp; Bookings API</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>HIGH-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Role Escalation Protection Active on User Registration</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HIGH-04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Strict Booking Status Transition Validation Enforced</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MED-01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Insecure Session Management</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>API Key Scope Restricted &amp; Service Keys Vaulted</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Source Control</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MED-02</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Password Policy Enforces Complexity &amp; Leaked DB Check</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-17 14:58:08</t>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MED-03</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>File Type &amp; Extension Restrictions on Storage Uploads</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LOW-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Sanitized Exception Errors Returned to API Clients</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LOW-02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Application Rate Limiting Active on Auth Endpoints</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 11:54:13</t>
         </is>
       </c>
     </row>
